--- a/inputs/templates/TEMPLATE_FONDO_LIQUIDEZ_Disponible_I.xlsx
+++ b/inputs/templates/TEMPLATE_FONDO_LIQUIDEZ_Disponible_I.xlsx
@@ -24,7 +24,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="9">
+  <numFmts count="10">
     <numFmt numFmtId="164" formatCode="#,##0.0000"/>
     <numFmt numFmtId="165" formatCode="0.0000"/>
     <numFmt numFmtId="166" formatCode="#,##0.00_ ;[Red]\-#,##0.00\ "/>
@@ -34,6 +34,7 @@
     <numFmt numFmtId="170" formatCode="_ * #,##0.000_ ;_ * \-#,##0.000_ ;_ * &quot;-&quot;_ ;_ @_ "/>
     <numFmt numFmtId="171" formatCode="0.000%"/>
     <numFmt numFmtId="172" formatCode="[$$-1004]#,##0"/>
+    <numFmt numFmtId="173" formatCode="yyyy-mm-dd h:mm:ss"/>
   </numFmts>
   <fonts count="31">
     <font>
@@ -468,7 +469,7 @@
     <xf numFmtId="169" fontId="7" fillId="0" borderId="0"/>
     <xf numFmtId="169" fontId="5" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="122">
+  <cellXfs count="123">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -699,6 +700,7 @@
     <xf numFmtId="169" fontId="6" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="7"/>
     <xf numFmtId="169" fontId="6" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="1"/>
     <xf numFmtId="171" fontId="22" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="6"/>
+    <xf numFmtId="173" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="61">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -2188,7 +2190,7 @@
               </a:defRPr>
             </a:pPr>
             <a:r>
-              <a:t/>
+              <a:t>None</a:t>
             </a:r>
             <a:endParaRPr lang="es-CL"/>
           </a:p>
@@ -2240,7 +2242,7 @@
               </a:defRPr>
             </a:pPr>
             <a:r>
-              <a:t/>
+              <a:t>None</a:t>
             </a:r>
             <a:endParaRPr lang="es-CL"/>
           </a:p>
@@ -2335,7 +2337,7 @@
             </a:defRPr>
           </a:pPr>
           <a:r>
-            <a:t/>
+            <a:t>None</a:t>
           </a:r>
           <a:endParaRPr lang="es-CL"/>
         </a:p>
@@ -2824,7 +2826,7 @@
                 </a:defRPr>
               </a:pPr>
               <a:r>
-                <a:t/>
+                <a:t>None</a:t>
               </a:r>
               <a:endParaRPr lang="es-CL"/>
             </a:p>
@@ -2856,7 +2858,7 @@
               </a:defRPr>
             </a:pPr>
             <a:r>
-              <a:t/>
+              <a:t>None</a:t>
             </a:r>
             <a:endParaRPr lang="es-CL"/>
           </a:p>
@@ -2893,7 +2895,7 @@
             </a:defRPr>
           </a:pPr>
           <a:r>
-            <a:t/>
+            <a:t>None</a:t>
           </a:r>
           <a:endParaRPr lang="es-CL"/>
         </a:p>
@@ -6319,7 +6321,7 @@
         </is>
       </c>
       <c r="AW19" s="79" t="n">
-        <v>46142</v>
+        <v>46144</v>
       </c>
       <c r="AX19" s="37">
         <f>EOMONTH($AW19,AX18)+6</f>
@@ -15222,7 +15224,48 @@
         <v/>
       </c>
     </row>
-    <row r="250"/>
+    <row r="250">
+      <c r="A250" s="122" t="n">
+        <v>46144</v>
+      </c>
+      <c r="B250" t="n">
+        <v>19991.53842678169</v>
+      </c>
+      <c r="C250">
+        <f>(B250/B249-1)/(A250-A249)*30</f>
+        <v/>
+      </c>
+      <c r="D250">
+        <f>+D249*(1+C250)</f>
+        <v/>
+      </c>
+      <c r="F250" s="122" t="n">
+        <v>46144</v>
+      </c>
+      <c r="G250" t="n">
+        <v>1120.2873</v>
+      </c>
+      <c r="H250">
+        <f>+G250+$S$148+$S$150+$S$152+$S$154+$S$156+$S$158</f>
+        <v/>
+      </c>
+      <c r="I250">
+        <f>+(H250/H249-1)/(F250-F249)*30</f>
+        <v/>
+      </c>
+      <c r="J250">
+        <f>+J249*(1+I250)</f>
+        <v/>
+      </c>
+      <c r="L250">
+        <f>+(K250/K249-1)/(F250-F249)*30</f>
+        <v/>
+      </c>
+      <c r="M250">
+        <f>+M249*(1+L250)</f>
+        <v/>
+      </c>
+    </row>
     <row r="251"/>
     <row r="252"/>
     <row r="253"/>
